--- a/rmonize/data_proc_elem/DPE_LISA_P1.xlsx
+++ b/rmonize/data_proc_elem/DPE_LISA_P1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20415"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Projekte\NFDI4Health\TA5\Pilotprojekte\Harmonisierung\HarmonizR\use-cases-harmonisation\rmonize\data_proc_elem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{12D2F8EC-5124-4816-9BE9-70D96A8BD0D7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F54842-1D9A-4767-9CAD-1E9759DCC8AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="22260" windowHeight="12000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_processing_elements_templa" sheetId="1" r:id="rId1"/>
@@ -111,25 +111,6 @@
     <t>case_when</t>
   </si>
   <si>
-    <t>case_when(
-      MUTBILD_0 == 1 &amp; VATBILD_0 == 1 ~ 0L,
-      MUTBILD_0 %in% c(2) | VATBILD_0 %in% c(2) ~ 1L,  
-      MUTBILD_0 %in% c(3) | VATBILD_0 %in% c(3) ~ 2L, 
-      MUTBILD_0 %in% c(4) | VATBILD_0 %in% c(4) ~ 3L, 
-      MUTBILD_0 %in% c(5, 6) | VATBILD_0 %in% c(5, 6) ~ 4L, 
-      MUTBILD_0 %in% c(7) | VATBILD_0 %in% c(7) ~ 5L,  
-      TRUE ~ NA_integer_ 
-    )</t>
-  </si>
-  <si>
-    <t>"None" (0): Both parents have 1 (no certificate).
-"Primary School Completed" (1): Either parent has 2.
-"Technical/Professional School" (2): Either parent has 3.
-"Secondary School" (3): Either parent has 4.
-"Longer Education" (4): Either parent has 5 or 6.
-"Not Specified" (5): Either parent has 7 (other degree).</t>
-  </si>
-  <si>
     <t>compatible</t>
   </si>
   <si>
@@ -1306,6 +1287,25 @@
   </si>
   <si>
     <t>K_FB_alkgetr_cocktail_15;K_FB_alkgetr_alkopops_15;</t>
+  </si>
+  <si>
+    <t>case_when(
+      MUTBILD_0 == 1 &amp; VATBILD_0 == 1 ~ 0L,
+      MUTBILD_0 %in% c(2) | VATBILD_0 %in% c(2) ~ 1L,  
+      MUTBILD_0 %in% c(3) | VATBILD_0 %in% c(3) ~ 3L, 
+      MUTBILD_0 %in% c(4) | VATBILD_0 %in% c(4) ~ 2L, 
+      MUTBILD_0 %in% c(5, 6) | VATBILD_0 %in% c(5, 6) ~ 4L, 
+      MUTBILD_0 %in% c(7) | VATBILD_0 %in% c(7) ~ 5L,  
+      TRUE ~ NA_integer_
+    )</t>
+  </si>
+  <si>
+    <t>"None" (0): Both parents have 1 (no certificate).
+"Primary School Completed" (1): Either parent has 2.
+"Technical/Professional School" (2): Either parent has 4.
+"Secondary School" (3): Either parent has 3.
+"Longer Education" (4): Either parent has 5 or 6.
+"Not Specified" (5): Either parent has 7 (other degree).</t>
   </si>
 </sst>
 </file>
@@ -1841,7 +1841,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1899,51 +1899,54 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
-    <cellStyle name="20 % - Akzent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20 % - Akzent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20 % - Akzent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20 % - Akzent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20 % - Akzent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20 % - Akzent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40 % - Akzent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40 % - Akzent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40 % - Akzent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40 % - Akzent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40 % - Akzent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40 % - Akzent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60 % - Akzent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60 % - Akzent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60 % - Akzent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60 % - Akzent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60 % - Akzent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60 % - Akzent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Akzent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Akzent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Akzent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Akzent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Akzent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Akzent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Ausgabe" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Berechnung" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Eingabe" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Ergebnis" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Erklärender Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Gut" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Link" xfId="42" builtinId="8"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Notiz" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Schlecht" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
-    <cellStyle name="Überschrift" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Überschrift 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Überschrift 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Überschrift 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Überschrift 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Verknüpfte Zelle" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Warnender Text" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="Zelle überprüfen" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1959,9 +1962,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1999,7 +2002,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2105,7 +2108,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2247,7 +2250,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2256,7 +2259,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K129"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="138.140625" bestFit="1" customWidth="1"/>
@@ -2378,10 +2381,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
@@ -2396,16 +2399,16 @@
         <v>21</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="J4" s="12" t="s">
         <v>16</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="240" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2422,22 +2425,22 @@
         <v>14</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="26" t="s">
-        <v>28</v>
+      <c r="H5" s="27" t="s">
+        <v>391</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>29</v>
+        <v>392</v>
       </c>
       <c r="J5" s="12" t="s">
         <v>16</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="105" x14ac:dyDescent="0.25">
@@ -2445,34 +2448,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>356</v>
+      </c>
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="G6" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C6" t="s">
-        <v>358</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="H6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="G6" s="12" t="s">
+      <c r="I6" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>35</v>
       </c>
       <c r="J6" s="12" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -2480,10 +2483,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
@@ -2492,20 +2495,20 @@
         <v>14</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -2513,19 +2516,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G8" s="13" t="s">
         <v>21</v>
@@ -2546,25 +2549,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C9" t="s">
+      <c r="G9" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>46</v>
-      </c>
       <c r="H9" s="26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I9" s="13"/>
       <c r="J9" s="13" t="s">
@@ -2579,34 +2582,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C10" t="s">
+      <c r="I10" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10" s="4" t="s">
+      <c r="J10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -2614,31 +2617,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -2646,31 +2649,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="D12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -2678,31 +2681,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="C13" t="s">
-        <v>59</v>
-      </c>
-      <c r="D13" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>60</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -2710,31 +2713,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="C14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>63</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -2742,19 +2745,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>64</v>
-      </c>
-      <c r="C15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>21</v>
@@ -2774,19 +2777,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>67</v>
-      </c>
-      <c r="C16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>21</v>
@@ -2806,22 +2809,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C17" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>72</v>
-      </c>
       <c r="G17" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>21</v>
@@ -2838,31 +2841,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E18" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -2870,31 +2873,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E19" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -2902,31 +2905,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E20" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -2934,31 +2937,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E21" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -2966,31 +2969,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D22" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E22" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -2998,31 +3001,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D23" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E23" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -3030,31 +3033,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D24" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E24" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -3062,32 +3065,32 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="C25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D25" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -3095,31 +3098,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="C26" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26" t="s">
-        <v>32</v>
-      </c>
-      <c r="E26" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>92</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -3127,31 +3130,31 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E27" t="s">
         <v>14</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -3159,31 +3162,31 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D28" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E28" t="s">
         <v>14</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -3191,31 +3194,31 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D29" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E29" t="s">
         <v>14</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -3223,31 +3226,31 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" t="s">
+        <v>98</v>
+      </c>
+      <c r="D30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H30" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="C30" t="s">
-        <v>100</v>
-      </c>
-      <c r="D30" t="s">
-        <v>32</v>
-      </c>
-      <c r="E30" t="s">
-        <v>14</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>101</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -3255,19 +3258,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" t="s">
+        <v>101</v>
+      </c>
+      <c r="D31" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31" s="8" t="s">
         <v>102</v>
-      </c>
-      <c r="C31" t="s">
-        <v>103</v>
-      </c>
-      <c r="D31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E31" t="s">
-        <v>14</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>104</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>21</v>
@@ -3287,31 +3290,31 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" t="s">
+        <v>14</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H32" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="C32" t="s">
-        <v>106</v>
-      </c>
-      <c r="D32" t="s">
-        <v>32</v>
-      </c>
-      <c r="E32" t="s">
-        <v>14</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>107</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -3319,19 +3322,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" s="8" t="s">
         <v>108</v>
-      </c>
-      <c r="C33" t="s">
-        <v>109</v>
-      </c>
-      <c r="D33" t="s">
-        <v>32</v>
-      </c>
-      <c r="E33" t="s">
-        <v>14</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>110</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>21</v>
@@ -3351,19 +3354,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C34" t="s">
+        <v>110</v>
+      </c>
+      <c r="D34" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" t="s">
+        <v>14</v>
+      </c>
+      <c r="F34" s="8" t="s">
         <v>111</v>
-      </c>
-      <c r="C34" t="s">
-        <v>112</v>
-      </c>
-      <c r="D34" t="s">
-        <v>32</v>
-      </c>
-      <c r="E34" t="s">
-        <v>14</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>21</v>
@@ -3384,32 +3387,32 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C35" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D35" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E35" t="s">
         <v>14</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I35" s="2"/>
       <c r="J35" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K35" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -3417,19 +3420,19 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C36" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D36" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E36" t="s">
         <v>14</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>21</v>
@@ -3450,19 +3453,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C37" t="s">
+        <v>117</v>
+      </c>
+      <c r="D37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="C37" t="s">
-        <v>119</v>
-      </c>
-      <c r="D37" t="s">
-        <v>32</v>
-      </c>
-      <c r="E37" t="s">
-        <v>14</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>120</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>21</v>
@@ -3483,19 +3486,19 @@
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C38" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D38" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E38" t="s">
         <v>14</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>21</v>
@@ -3516,31 +3519,31 @@
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C39" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D39" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E39" t="s">
         <v>14</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -3548,31 +3551,31 @@
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C40" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D40" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E40" t="s">
         <v>14</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -3580,31 +3583,31 @@
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D41" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E41" t="s">
         <v>14</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -3612,31 +3615,31 @@
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C42" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D42" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E42" t="s">
         <v>14</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -3644,31 +3647,31 @@
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C43" t="s">
+        <v>129</v>
+      </c>
+      <c r="D43" t="s">
+        <v>30</v>
+      </c>
+      <c r="E43" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H43" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="C43" t="s">
-        <v>131</v>
-      </c>
-      <c r="D43" t="s">
-        <v>32</v>
-      </c>
-      <c r="E43" t="s">
-        <v>14</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>132</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -3676,34 +3679,34 @@
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C44" t="s">
+        <v>132</v>
+      </c>
+      <c r="D44" t="s">
+        <v>30</v>
+      </c>
+      <c r="E44" t="s">
+        <v>14</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H44" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C44" t="s">
+      <c r="I44" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="D44" t="s">
-        <v>32</v>
-      </c>
-      <c r="E44" t="s">
-        <v>14</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="I44" s="7" t="s">
-        <v>136</v>
-      </c>
       <c r="J44" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -3711,31 +3714,31 @@
         <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C45" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D45" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E45" t="s">
         <v>14</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -3743,31 +3746,31 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C46" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D46" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E46" t="s">
         <v>14</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -3775,31 +3778,31 @@
         <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C47" t="s">
+        <v>140</v>
+      </c>
+      <c r="D47" t="s">
+        <v>30</v>
+      </c>
+      <c r="E47" t="s">
+        <v>14</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H47" s="4" t="s">
         <v>141</v>
-      </c>
-      <c r="C47" t="s">
-        <v>142</v>
-      </c>
-      <c r="D47" t="s">
-        <v>32</v>
-      </c>
-      <c r="E47" t="s">
-        <v>14</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -3807,31 +3810,31 @@
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C48" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D48" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E48" t="s">
         <v>14</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -3839,19 +3842,19 @@
         <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C49" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D49" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E49" t="s">
         <v>14</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>21</v>
@@ -3871,19 +3874,19 @@
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C50" t="s">
+        <v>147</v>
+      </c>
+      <c r="D50" t="s">
+        <v>30</v>
+      </c>
+      <c r="E50" t="s">
+        <v>14</v>
+      </c>
+      <c r="F50" s="21" t="s">
         <v>148</v>
-      </c>
-      <c r="C50" t="s">
-        <v>149</v>
-      </c>
-      <c r="D50" t="s">
-        <v>32</v>
-      </c>
-      <c r="E50" t="s">
-        <v>14</v>
-      </c>
-      <c r="F50" s="21" t="s">
-        <v>150</v>
       </c>
       <c r="G50" s="21" t="s">
         <v>21</v>
@@ -3904,32 +3907,32 @@
         <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C51" t="s">
+        <v>150</v>
+      </c>
+      <c r="D51" t="s">
+        <v>30</v>
+      </c>
+      <c r="E51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F51" s="23" t="s">
+        <v>374</v>
+      </c>
+      <c r="G51" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="H51" s="21" t="s">
         <v>151</v>
-      </c>
-      <c r="C51" t="s">
-        <v>152</v>
-      </c>
-      <c r="D51" t="s">
-        <v>32</v>
-      </c>
-      <c r="E51" t="s">
-        <v>14</v>
-      </c>
-      <c r="F51" s="23" t="s">
-        <v>376</v>
-      </c>
-      <c r="G51" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="H51" s="21" t="s">
-        <v>153</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="21" t="s">
         <v>16</v>
       </c>
       <c r="K51" s="21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -3937,34 +3940,34 @@
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C52" t="s">
+        <v>153</v>
+      </c>
+      <c r="D52" t="s">
+        <v>30</v>
+      </c>
+      <c r="E52" t="s">
+        <v>14</v>
+      </c>
+      <c r="F52" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="C52" t="s">
+      <c r="G52" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H52" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D52" t="s">
-        <v>32</v>
-      </c>
-      <c r="E52" t="s">
-        <v>14</v>
-      </c>
-      <c r="F52" s="8" t="s">
+      <c r="I52" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G52" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H52" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="J52" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -3972,34 +3975,34 @@
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C53" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D53" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E53" t="s">
         <v>14</v>
       </c>
       <c r="F53" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="I53" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G53" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H53" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="J53" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -4007,19 +4010,19 @@
         <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C54" t="s">
+        <v>160</v>
+      </c>
+      <c r="D54" t="s">
+        <v>30</v>
+      </c>
+      <c r="E54" t="s">
+        <v>14</v>
+      </c>
+      <c r="F54" s="8" t="s">
         <v>161</v>
-      </c>
-      <c r="C54" t="s">
-        <v>162</v>
-      </c>
-      <c r="D54" t="s">
-        <v>32</v>
-      </c>
-      <c r="E54" t="s">
-        <v>14</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>163</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>21</v>
@@ -4039,31 +4042,31 @@
         <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C55" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D55" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E55" t="s">
         <v>14</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -4071,31 +4074,31 @@
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C56" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D56" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E56" t="s">
         <v>14</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -4103,31 +4106,31 @@
         <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C57" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D57" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E57" t="s">
         <v>14</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -4135,19 +4138,19 @@
         <v>57</v>
       </c>
       <c r="B58" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C58" t="s">
+        <v>169</v>
+      </c>
+      <c r="D58" t="s">
+        <v>30</v>
+      </c>
+      <c r="E58" t="s">
+        <v>14</v>
+      </c>
+      <c r="F58" s="4" t="s">
         <v>170</v>
-      </c>
-      <c r="C58" t="s">
-        <v>171</v>
-      </c>
-      <c r="D58" t="s">
-        <v>32</v>
-      </c>
-      <c r="E58" t="s">
-        <v>14</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>172</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>21</v>
@@ -4167,31 +4170,31 @@
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C59" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D59" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E59" t="s">
         <v>14</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -4199,31 +4202,31 @@
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C60" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D60" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E60" t="s">
         <v>14</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -4231,31 +4234,31 @@
         <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C61" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D61" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E61" t="s">
         <v>14</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -4263,31 +4266,31 @@
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C62" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D62" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E62" t="s">
         <v>14</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -4295,31 +4298,31 @@
         <v>62</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C63" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D63" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E63" t="s">
         <v>14</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -4327,31 +4330,31 @@
         <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C64" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D64" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E64" t="s">
         <v>14</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -4359,31 +4362,31 @@
         <v>64</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C65" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D65" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E65" t="s">
         <v>14</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -4391,31 +4394,31 @@
         <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C66" t="s">
+        <v>184</v>
+      </c>
+      <c r="D66" t="s">
+        <v>30</v>
+      </c>
+      <c r="E66" t="s">
+        <v>14</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H66" s="4" t="s">
         <v>185</v>
-      </c>
-      <c r="C66" t="s">
-        <v>186</v>
-      </c>
-      <c r="D66" t="s">
-        <v>32</v>
-      </c>
-      <c r="E66" t="s">
-        <v>14</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H66" s="4" t="s">
-        <v>187</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -4423,19 +4426,19 @@
         <v>66</v>
       </c>
       <c r="B67" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C67" t="s">
+        <v>187</v>
+      </c>
+      <c r="D67" t="s">
+        <v>30</v>
+      </c>
+      <c r="E67" t="s">
+        <v>14</v>
+      </c>
+      <c r="F67" s="8" t="s">
         <v>188</v>
-      </c>
-      <c r="C67" t="s">
-        <v>189</v>
-      </c>
-      <c r="D67" t="s">
-        <v>32</v>
-      </c>
-      <c r="E67" t="s">
-        <v>14</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>190</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>21</v>
@@ -4455,31 +4458,31 @@
         <v>67</v>
       </c>
       <c r="B68" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C68" t="s">
+        <v>190</v>
+      </c>
+      <c r="D68" t="s">
+        <v>30</v>
+      </c>
+      <c r="E68" t="s">
+        <v>14</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H68" s="4" t="s">
         <v>191</v>
-      </c>
-      <c r="C68" t="s">
-        <v>192</v>
-      </c>
-      <c r="D68" t="s">
-        <v>32</v>
-      </c>
-      <c r="E68" t="s">
-        <v>14</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H68" s="4" t="s">
-        <v>193</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -4487,31 +4490,31 @@
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C69" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D69" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E69" t="s">
         <v>14</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -4519,31 +4522,31 @@
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C70" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D70" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E70" t="s">
         <v>14</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -4551,31 +4554,31 @@
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C71" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D71" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E71" t="s">
         <v>14</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -4583,19 +4586,19 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
+        <v>198</v>
+      </c>
+      <c r="C72" t="s">
+        <v>199</v>
+      </c>
+      <c r="D72" t="s">
+        <v>30</v>
+      </c>
+      <c r="E72" t="s">
+        <v>14</v>
+      </c>
+      <c r="F72" s="8" t="s">
         <v>200</v>
-      </c>
-      <c r="C72" t="s">
-        <v>201</v>
-      </c>
-      <c r="D72" t="s">
-        <v>32</v>
-      </c>
-      <c r="E72" t="s">
-        <v>14</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>202</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>21</v>
@@ -4616,31 +4619,31 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C73" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D73" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E73" t="s">
         <v>14</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -4648,31 +4651,31 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
+        <v>203</v>
+      </c>
+      <c r="C74" t="s">
+        <v>204</v>
+      </c>
+      <c r="D74" t="s">
+        <v>30</v>
+      </c>
+      <c r="E74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H74" s="4" t="s">
         <v>205</v>
-      </c>
-      <c r="C74" t="s">
-        <v>206</v>
-      </c>
-      <c r="D74" t="s">
-        <v>32</v>
-      </c>
-      <c r="E74" t="s">
-        <v>14</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>207</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -4680,31 +4683,31 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
+        <v>206</v>
+      </c>
+      <c r="C75" t="s">
+        <v>207</v>
+      </c>
+      <c r="D75" t="s">
+        <v>30</v>
+      </c>
+      <c r="E75" t="s">
+        <v>14</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H75" s="4" t="s">
         <v>208</v>
-      </c>
-      <c r="C75" t="s">
-        <v>209</v>
-      </c>
-      <c r="D75" t="s">
-        <v>32</v>
-      </c>
-      <c r="E75" t="s">
-        <v>14</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>210</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -4712,31 +4715,31 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
+        <v>209</v>
+      </c>
+      <c r="C76" t="s">
+        <v>210</v>
+      </c>
+      <c r="D76" t="s">
+        <v>30</v>
+      </c>
+      <c r="E76" t="s">
+        <v>14</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H76" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="C76" t="s">
-        <v>212</v>
-      </c>
-      <c r="D76" t="s">
-        <v>32</v>
-      </c>
-      <c r="E76" t="s">
-        <v>14</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>213</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -4744,31 +4747,31 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
+        <v>212</v>
+      </c>
+      <c r="C77" t="s">
+        <v>213</v>
+      </c>
+      <c r="D77" t="s">
+        <v>30</v>
+      </c>
+      <c r="E77" t="s">
+        <v>14</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H77" s="4" t="s">
         <v>214</v>
-      </c>
-      <c r="C77" t="s">
-        <v>215</v>
-      </c>
-      <c r="D77" t="s">
-        <v>32</v>
-      </c>
-      <c r="E77" t="s">
-        <v>14</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H77" s="4" t="s">
-        <v>216</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -4776,31 +4779,31 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C78" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D78" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E78" t="s">
         <v>14</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -4808,31 +4811,31 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C79" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D79" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E79" t="s">
         <v>14</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -4840,31 +4843,31 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C80" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D80" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E80" t="s">
         <v>14</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -4872,31 +4875,31 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
+        <v>221</v>
+      </c>
+      <c r="C81" t="s">
+        <v>222</v>
+      </c>
+      <c r="D81" t="s">
+        <v>30</v>
+      </c>
+      <c r="E81" t="s">
+        <v>14</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H81" s="4" t="s">
         <v>223</v>
-      </c>
-      <c r="C81" t="s">
-        <v>224</v>
-      </c>
-      <c r="D81" t="s">
-        <v>32</v>
-      </c>
-      <c r="E81" t="s">
-        <v>14</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H81" s="4" t="s">
-        <v>225</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -4904,31 +4907,31 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C82" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D82" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E82" t="s">
         <v>14</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -4936,31 +4939,31 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C83" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D83" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E83" t="s">
         <v>14</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -4968,19 +4971,19 @@
         <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C84" t="s">
+        <v>229</v>
+      </c>
+      <c r="D84" t="s">
+        <v>30</v>
+      </c>
+      <c r="E84" t="s">
+        <v>14</v>
+      </c>
+      <c r="F84" s="4" t="s">
         <v>230</v>
-      </c>
-      <c r="C84" t="s">
-        <v>231</v>
-      </c>
-      <c r="D84" t="s">
-        <v>32</v>
-      </c>
-      <c r="E84" t="s">
-        <v>14</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>232</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>21</v>
@@ -5000,19 +5003,19 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
+        <v>231</v>
+      </c>
+      <c r="C85" t="s">
+        <v>232</v>
+      </c>
+      <c r="D85" t="s">
+        <v>30</v>
+      </c>
+      <c r="E85" t="s">
+        <v>14</v>
+      </c>
+      <c r="F85" s="4" t="s">
         <v>233</v>
-      </c>
-      <c r="C85" t="s">
-        <v>234</v>
-      </c>
-      <c r="D85" t="s">
-        <v>32</v>
-      </c>
-      <c r="E85" t="s">
-        <v>14</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>235</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>21</v>
@@ -5032,19 +5035,19 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
+        <v>234</v>
+      </c>
+      <c r="C86" t="s">
+        <v>235</v>
+      </c>
+      <c r="D86" t="s">
+        <v>30</v>
+      </c>
+      <c r="E86" t="s">
+        <v>14</v>
+      </c>
+      <c r="F86" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="C86" t="s">
-        <v>237</v>
-      </c>
-      <c r="D86" t="s">
-        <v>32</v>
-      </c>
-      <c r="E86" t="s">
-        <v>14</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>238</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>21</v>
@@ -5065,31 +5068,31 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D87" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E87" t="s">
         <v>14</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -5097,31 +5100,31 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C88" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D88" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E88" t="s">
         <v>14</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -5129,31 +5132,31 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C89" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D89" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E89" t="s">
         <v>14</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -5161,31 +5164,31 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C90" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D90" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E90" t="s">
         <v>14</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -5193,31 +5196,31 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
+        <v>245</v>
+      </c>
+      <c r="C91" t="s">
+        <v>246</v>
+      </c>
+      <c r="D91" t="s">
+        <v>30</v>
+      </c>
+      <c r="E91" t="s">
+        <v>14</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H91" s="4" t="s">
         <v>247</v>
-      </c>
-      <c r="C91" t="s">
-        <v>248</v>
-      </c>
-      <c r="D91" t="s">
-        <v>32</v>
-      </c>
-      <c r="E91" t="s">
-        <v>14</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>249</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -5225,19 +5228,19 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
+        <v>248</v>
+      </c>
+      <c r="C92" t="s">
+        <v>249</v>
+      </c>
+      <c r="D92" t="s">
+        <v>30</v>
+      </c>
+      <c r="E92" t="s">
+        <v>14</v>
+      </c>
+      <c r="F92" s="4" t="s">
         <v>250</v>
-      </c>
-      <c r="C92" t="s">
-        <v>251</v>
-      </c>
-      <c r="D92" t="s">
-        <v>32</v>
-      </c>
-      <c r="E92" t="s">
-        <v>14</v>
-      </c>
-      <c r="F92" s="4" t="s">
-        <v>252</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>21</v>
@@ -5257,31 +5260,31 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
+        <v>251</v>
+      </c>
+      <c r="C93" t="s">
+        <v>252</v>
+      </c>
+      <c r="D93" t="s">
+        <v>30</v>
+      </c>
+      <c r="E93" t="s">
+        <v>14</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H93" s="4" t="s">
         <v>253</v>
-      </c>
-      <c r="C93" t="s">
-        <v>254</v>
-      </c>
-      <c r="D93" t="s">
-        <v>32</v>
-      </c>
-      <c r="E93" t="s">
-        <v>14</v>
-      </c>
-      <c r="F93" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H93" s="4" t="s">
-        <v>255</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -5289,31 +5292,31 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
+        <v>254</v>
+      </c>
+      <c r="C94" t="s">
+        <v>255</v>
+      </c>
+      <c r="D94" t="s">
+        <v>30</v>
+      </c>
+      <c r="E94" t="s">
+        <v>14</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H94" s="4" t="s">
         <v>256</v>
-      </c>
-      <c r="C94" t="s">
-        <v>257</v>
-      </c>
-      <c r="D94" t="s">
-        <v>32</v>
-      </c>
-      <c r="E94" t="s">
-        <v>14</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H94" s="4" t="s">
-        <v>258</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -5321,31 +5324,31 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
+        <v>257</v>
+      </c>
+      <c r="C95" t="s">
+        <v>258</v>
+      </c>
+      <c r="D95" t="s">
+        <v>30</v>
+      </c>
+      <c r="E95" t="s">
+        <v>14</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H95" s="4" t="s">
         <v>259</v>
-      </c>
-      <c r="C95" t="s">
-        <v>260</v>
-      </c>
-      <c r="D95" t="s">
-        <v>32</v>
-      </c>
-      <c r="E95" t="s">
-        <v>14</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H95" s="4" t="s">
-        <v>261</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -5353,19 +5356,19 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
+        <v>260</v>
+      </c>
+      <c r="C96" t="s">
+        <v>261</v>
+      </c>
+      <c r="D96" t="s">
+        <v>30</v>
+      </c>
+      <c r="E96" t="s">
+        <v>14</v>
+      </c>
+      <c r="F96" s="4" t="s">
         <v>262</v>
-      </c>
-      <c r="C96" t="s">
-        <v>263</v>
-      </c>
-      <c r="D96" t="s">
-        <v>32</v>
-      </c>
-      <c r="E96" t="s">
-        <v>14</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>264</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>21</v>
@@ -5374,13 +5377,13 @@
         <v>21</v>
       </c>
       <c r="I96" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="J96" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K96" s="21" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -5388,31 +5391,31 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C97" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D97" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E97" t="s">
         <v>14</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -5420,19 +5423,19 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C98" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D98" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E98" t="s">
         <v>14</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>21</v>
@@ -5452,31 +5455,31 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C99" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D99" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E99" t="s">
         <v>14</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -5484,31 +5487,31 @@
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C100" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D100" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E100" t="s">
         <v>14</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -5516,19 +5519,19 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
+        <v>273</v>
+      </c>
+      <c r="C101" t="s">
+        <v>274</v>
+      </c>
+      <c r="D101" t="s">
+        <v>30</v>
+      </c>
+      <c r="E101" t="s">
+        <v>14</v>
+      </c>
+      <c r="F101" s="8" t="s">
         <v>275</v>
-      </c>
-      <c r="C101" t="s">
-        <v>276</v>
-      </c>
-      <c r="D101" t="s">
-        <v>32</v>
-      </c>
-      <c r="E101" t="s">
-        <v>14</v>
-      </c>
-      <c r="F101" s="8" t="s">
-        <v>277</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>21</v>
@@ -5548,19 +5551,19 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
+        <v>276</v>
+      </c>
+      <c r="C102" t="s">
+        <v>277</v>
+      </c>
+      <c r="D102" t="s">
+        <v>30</v>
+      </c>
+      <c r="E102" t="s">
+        <v>14</v>
+      </c>
+      <c r="F102" s="15" t="s">
         <v>278</v>
-      </c>
-      <c r="C102" t="s">
-        <v>279</v>
-      </c>
-      <c r="D102" t="s">
-        <v>32</v>
-      </c>
-      <c r="E102" t="s">
-        <v>14</v>
-      </c>
-      <c r="F102" s="15" t="s">
-        <v>280</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>21</v>
@@ -5580,19 +5583,19 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
+        <v>279</v>
+      </c>
+      <c r="C103" t="s">
+        <v>280</v>
+      </c>
+      <c r="D103" t="s">
+        <v>30</v>
+      </c>
+      <c r="E103" t="s">
+        <v>14</v>
+      </c>
+      <c r="F103" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="C103" t="s">
-        <v>282</v>
-      </c>
-      <c r="D103" t="s">
-        <v>32</v>
-      </c>
-      <c r="E103" t="s">
-        <v>14</v>
-      </c>
-      <c r="F103" s="4" t="s">
-        <v>283</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>21</v>
@@ -5612,31 +5615,31 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C104" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D104" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E104" t="s">
         <v>14</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -5644,19 +5647,19 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
+        <v>284</v>
+      </c>
+      <c r="C105" t="s">
+        <v>285</v>
+      </c>
+      <c r="D105" t="s">
+        <v>30</v>
+      </c>
+      <c r="E105" t="s">
+        <v>14</v>
+      </c>
+      <c r="F105" s="4" t="s">
         <v>286</v>
-      </c>
-      <c r="C105" t="s">
-        <v>287</v>
-      </c>
-      <c r="D105" t="s">
-        <v>32</v>
-      </c>
-      <c r="E105" t="s">
-        <v>14</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>288</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>21</v>
@@ -5676,31 +5679,31 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C106" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D106" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E106" t="s">
         <v>14</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
@@ -5708,31 +5711,31 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C107" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D107" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E107" t="s">
         <v>14</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
@@ -5740,19 +5743,19 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
+        <v>291</v>
+      </c>
+      <c r="C108" t="s">
+        <v>292</v>
+      </c>
+      <c r="D108" t="s">
+        <v>30</v>
+      </c>
+      <c r="E108" t="s">
+        <v>14</v>
+      </c>
+      <c r="F108" s="4" t="s">
         <v>293</v>
-      </c>
-      <c r="C108" t="s">
-        <v>294</v>
-      </c>
-      <c r="D108" t="s">
-        <v>32</v>
-      </c>
-      <c r="E108" t="s">
-        <v>14</v>
-      </c>
-      <c r="F108" s="4" t="s">
-        <v>295</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>21</v>
@@ -5772,34 +5775,34 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
+        <v>294</v>
+      </c>
+      <c r="C109" t="s">
+        <v>295</v>
+      </c>
+      <c r="D109" t="s">
+        <v>30</v>
+      </c>
+      <c r="E109" t="s">
+        <v>14</v>
+      </c>
+      <c r="F109" s="24" t="s">
+        <v>390</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H109" s="15" t="s">
         <v>296</v>
       </c>
-      <c r="C109" t="s">
+      <c r="I109" s="6" t="s">
         <v>297</v>
-      </c>
-      <c r="D109" t="s">
-        <v>32</v>
-      </c>
-      <c r="E109" t="s">
-        <v>14</v>
-      </c>
-      <c r="F109" s="24" t="s">
-        <v>392</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H109" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="I109" s="6" t="s">
-        <v>299</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
@@ -5807,31 +5810,31 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C110" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D110" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E110" t="s">
         <v>14</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -5839,31 +5842,31 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C111" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D111" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E111" t="s">
         <v>14</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -5871,31 +5874,31 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C112" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D112" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E112" t="s">
         <v>14</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -5903,31 +5906,31 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C113" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D113" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E113" t="s">
         <v>14</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -5935,31 +5938,31 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C114" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D114" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E114" t="s">
         <v>14</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
@@ -5967,31 +5970,31 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C115" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D115" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E115" t="s">
         <v>14</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K115" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -5999,31 +6002,31 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C116" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D116" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E116" t="s">
         <v>14</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -6031,31 +6034,31 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C117" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D117" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E117" t="s">
         <v>14</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -6063,31 +6066,31 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C118" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D118" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E118" t="s">
         <v>14</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -6095,31 +6098,31 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C119" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D119" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E119" t="s">
         <v>14</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -6127,31 +6130,31 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C120" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D120" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E120" t="s">
         <v>14</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -6159,31 +6162,31 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C121" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D121" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E121" t="s">
         <v>14</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
@@ -6191,31 +6194,31 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C122" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D122" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E122" t="s">
         <v>14</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K122" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -6223,31 +6226,31 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C123" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D123" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E123" t="s">
         <v>14</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K123" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
@@ -6255,31 +6258,31 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C124" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D124" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E124" t="s">
         <v>14</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K124" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
@@ -6287,31 +6290,31 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C125" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D125" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E125" t="s">
         <v>14</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K125" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
@@ -6319,31 +6322,31 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C126" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D126" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E126" t="s">
         <v>14</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K126" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -6351,19 +6354,19 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
+        <v>330</v>
+      </c>
+      <c r="C127" t="s">
+        <v>331</v>
+      </c>
+      <c r="D127" t="s">
+        <v>30</v>
+      </c>
+      <c r="E127" t="s">
+        <v>14</v>
+      </c>
+      <c r="F127" s="4" t="s">
         <v>332</v>
-      </c>
-      <c r="C127" t="s">
-        <v>333</v>
-      </c>
-      <c r="D127" t="s">
-        <v>32</v>
-      </c>
-      <c r="E127" t="s">
-        <v>14</v>
-      </c>
-      <c r="F127" s="4" t="s">
-        <v>334</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>21</v>
@@ -6383,31 +6386,31 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C128" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D128" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E128" t="s">
         <v>14</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K128" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
@@ -6415,10 +6418,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C129" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D129" t="s">
         <v>13</v>
@@ -6427,16 +6430,16 @@
         <v>14</v>
       </c>
       <c r="F129" s="20" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H129" s="18">
         <v>1</v>
       </c>
       <c r="I129" s="16" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="J129" s="17" t="s">
         <v>16</v>
@@ -6697,6 +6700,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Zeit xmlns="b63cdcf7-47fa-43f6-87e5-23b415b5c413" xsi:nil="true"/>
@@ -6706,15 +6718,6 @@
     <TaxCatchAll xmlns="12535b08-222e-45d2-b6db-15019f1afee6" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6737,6 +6740,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E89B3EC5-962B-41D9-9821-3A191D2434CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBFC15CC-4CA5-447A-915F-1412CED97222}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -6751,12 +6762,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E89B3EC5-962B-41D9-9821-3A191D2434CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/rmonize/data_proc_elem/DPE_LISA_P1.xlsx
+++ b/rmonize/data_proc_elem/DPE_LISA_P1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F54842-1D9A-4767-9CAD-1E9759DCC8AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C4AFFB-BF15-49AD-B498-31C3584DB89F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="22260" windowHeight="12000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11025" yWindow="0" windowWidth="11025" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_processing_elements_templa" sheetId="1" r:id="rId1"/>
@@ -1290,21 +1290,19 @@
   </si>
   <si>
     <t>case_when(
-      MUTBILD_0 == 1 &amp; VATBILD_0 == 1 ~ 0L,
-      MUTBILD_0 %in% c(2) | VATBILD_0 %in% c(2) ~ 1L,  
-      MUTBILD_0 %in% c(3) | VATBILD_0 %in% c(3) ~ 3L, 
-      MUTBILD_0 %in% c(4) | VATBILD_0 %in% c(4) ~ 2L, 
-      MUTBILD_0 %in% c(5, 6) | VATBILD_0 %in% c(5, 6) ~ 4L, 
-      MUTBILD_0 %in% c(7) | VATBILD_0 %in% c(7) ~ 5L,  
+      MUTBILD_0 %in% c(5, 6) | VATBILD_0 %in% c(5, 6) ~ 4L,
+      MUTBILD_0 %in% c(3,4) | VATBILD_0 %in% c(3,4) ~ 3L,
+      MUTBILD_0 %in% c(2) | VATBILD_0 %in% c(2) ~ 1L,
+      MUTBILD_0 == 1 | VATBILD_0 == 1 ~ 0L,
+      MUTBILD_0 %in% c(7) | VATBILD_0 %in% c(7) ~ 5L,
       TRUE ~ NA_integer_
     )</t>
   </si>
   <si>
-    <t>"None" (0): Both parents have 1 (no certificate).
+    <t>"Longer Education" (4): Either parent has 5 or 6.
+"Secondary School" (3): Either parent has 3 or 4.
 "Primary School Completed" (1): Either parent has 2.
-"Technical/Professional School" (2): Either parent has 4.
-"Secondary School" (3): Either parent has 3.
-"Longer Education" (4): Either parent has 5 or 6.
+"None" (0): Either parent has 1 (no certificate).
 "Not Specified" (5): Either parent has 7 (other degree).</t>
   </si>
 </sst>
@@ -1899,7 +1897,7 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2408,7 +2406,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="255" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -6459,6 +6457,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100B1DC67C611DD5E4D81775F9F3E26A7B2" ma:contentTypeVersion="16" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="7f379a5812b480a74f9d031be5f88a83">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b63cdcf7-47fa-43f6-87e5-23b415b5c413" xmlns:ns3="12535b08-222e-45d2-b6db-15019f1afee6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dbce1e37d7de67e1c835013ca0ee7a7c" ns2:_="" ns3:_="">
     <xsd:import namespace="b63cdcf7-47fa-43f6-87e5-23b415b5c413"/>
@@ -6699,15 +6706,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -6721,6 +6719,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E89B3EC5-962B-41D9-9821-3A191D2434CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA68FB6B-B5E6-4AB5-ACC7-06ACAB30D951}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6735,14 +6741,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E89B3EC5-962B-41D9-9821-3A191D2434CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/rmonize/data_proc_elem/DPE_LISA_P1.xlsx
+++ b/rmonize/data_proc_elem/DPE_LISA_P1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\rmonize\data_proc_elem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C4AFFB-BF15-49AD-B498-31C3584DB89F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7677C5CF-C35A-466D-B3B9-7ADB0B5934DA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11025" yWindow="0" windowWidth="11025" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1196,9 +1196,6 @@
     <t>FFQNUSS_15 + FFQKERN_15</t>
   </si>
   <si>
-    <t>MUTBILD_0;VATBILD_0;</t>
-  </si>
-  <si>
     <t>aktivleiisommn_15;aktivleiwintn_15;aktivmitsommn_15;aktivmitwintn_15;aktivschsommn_15;aktivschwintn_15</t>
   </si>
   <si>
@@ -1289,21 +1286,24 @@
     <t>K_FB_alkgetr_cocktail_15;K_FB_alkgetr_alkopops_15;</t>
   </si>
   <si>
+    <t>MUTBILD_0;VATBILD_0; MUTBERU_0; VATBERU_0</t>
+  </si>
+  <si>
     <t>case_when(
-      MUTBILD_0 %in% c(5, 6) | VATBILD_0 %in% c(5, 6) ~ 4L,
-      MUTBILD_0 %in% c(3,4) | VATBILD_0 %in% c(3,4) ~ 3L,
-      MUTBILD_0 %in% c(2) | VATBILD_0 %in% c(2) ~ 1L,
-      MUTBILD_0 == 1 | VATBILD_0 == 1 ~ 0L,
-      MUTBILD_0 %in% c(7) | VATBILD_0 %in% c(7) ~ 5L,
-      TRUE ~ NA_integer_
-    )</t>
-  </si>
-  <si>
-    <t>"Longer Education" (4): Either parent has 5 or 6.
-"Secondary School" (3): Either parent has 3 or 4.
-"Primary School Completed" (1): Either parent has 2.
-"None" (0): Either parent has 1 (no certificate).
-"Not Specified" (5): Either parent has 7 (other degree).</t>
+  MUTBERU_0 %in% c(7) | VATBERU_0 %in% c(7) ~ 7L,
+  MUTBERU_0 %in% c(5,6) | VATBERU_0 %in% c(5,6) ~ 6L,
+  MUTBERU_0 %in% c(3,4) |VATBERU_0 %in% c(3,4) ~ 4L,
+  MUTBERU_0 %in% c(8) |VATBERU_0 %in% c(8) ~ 9L,
+  MUTBILD_0 %in% c(5,6) | VATBILD_0 %in% c(5,6) ~ 3L,
+  MUTBILD_0 %in% c(2,3,4) | VATBILD_0 %in% c(2,3,4) ~ 2L,
+  MUTBILD_0 %in% c(1) &amp; VATBILD_0 %in% c(1) ~ 0L,
+  is.na(MUTBILD_0) &amp; VATBILD_0 %in% c(1) ~ 0L,
+  MUTBILD_0 %in% c(1) &amp; is.na(VATBILD_0) ~ 0L,
+  MUTBILD_0 %in% c(7) | VATBILD_0 %in% c(7) ~ 9L,
+  TRUE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>Education according to the ISCED 2011 classification</t>
   </si>
 </sst>
 </file>
@@ -1902,49 +1902,49 @@
     </xf>
   </cellXfs>
   <cellStyles count="43">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Akzent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Akzent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Akzent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Akzent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Akzent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Akzent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Ausgabe" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Berechnung" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Eingabe" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Ergebnis" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Erklärender Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Gut" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Link" xfId="42" builtinId="8"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Notiz" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Schlecht" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Überschrift" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Überschrift 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Überschrift 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Überschrift 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Überschrift 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Verknüpfte Zelle" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Warnender Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Zelle überprüfen" xfId="13" builtinId="23" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1960,9 +1960,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2000,7 +2000,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2106,7 +2106,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2248,7 +2248,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2257,14 +2257,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K129"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="138.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.5703125" style="18" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="129.42578125" style="18" customWidth="1"/>
     <col min="9" max="9" width="22.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="25.42578125" bestFit="1" customWidth="1"/>
@@ -2406,7 +2406,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="255" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="180" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>27</v>
@@ -2435,10 +2435,10 @@
         <v>392</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="105" x14ac:dyDescent="0.25">
@@ -2458,7 +2458,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>31</v>
@@ -2592,7 +2592,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>31</v>
@@ -2627,7 +2627,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>31</v>
@@ -2691,7 +2691,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>31</v>
@@ -2723,7 +2723,7 @@
         <v>14</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>31</v>
@@ -3075,7 +3075,7 @@
         <v>14</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>31</v>
@@ -3108,7 +3108,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>31</v>
@@ -3236,7 +3236,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>31</v>
@@ -3300,7 +3300,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>31</v>
@@ -3397,7 +3397,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>31</v>
@@ -3593,7 +3593,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>31</v>
@@ -3657,7 +3657,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>31</v>
@@ -3689,7 +3689,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>31</v>
@@ -3724,7 +3724,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>31</v>
@@ -3788,7 +3788,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>31</v>
@@ -3917,7 +3917,7 @@
         <v>14</v>
       </c>
       <c r="F51" s="23" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G51" s="21" t="s">
         <v>31</v>
@@ -4404,7 +4404,7 @@
         <v>14</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>31</v>
@@ -4468,7 +4468,7 @@
         <v>14</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>31</v>
@@ -4500,7 +4500,7 @@
         <v>14</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>31</v>
@@ -4564,7 +4564,7 @@
         <v>14</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>31</v>
@@ -4661,7 +4661,7 @@
         <v>14</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>31</v>
@@ -4693,7 +4693,7 @@
         <v>14</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>31</v>
@@ -4725,7 +4725,7 @@
         <v>14</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>31</v>
@@ -4757,7 +4757,7 @@
         <v>14</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>31</v>
@@ -4885,7 +4885,7 @@
         <v>14</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>31</v>
@@ -4949,7 +4949,7 @@
         <v>14</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>31</v>
@@ -5174,7 +5174,7 @@
         <v>14</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>31</v>
@@ -5206,7 +5206,7 @@
         <v>14</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>31</v>
@@ -5270,7 +5270,7 @@
         <v>14</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>31</v>
@@ -5302,7 +5302,7 @@
         <v>14</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>31</v>
@@ -5334,7 +5334,7 @@
         <v>14</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G95" s="4" t="s">
         <v>31</v>
@@ -5785,7 +5785,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="24" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>31</v>
